--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101571</v>
+        <v>101574</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>136114818</v>
       </c>
       <c r="B90" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>136114819</v>
       </c>
       <c r="B91" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136114825</v>
       </c>
       <c r="B92" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>136114826</v>
       </c>
       <c r="B93" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>136114821</v>
       </c>
       <c r="B112" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>136114827</v>
       </c>
       <c r="B113" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>136114824</v>
       </c>
       <c r="B115" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>136114817</v>
       </c>
       <c r="B131" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>136114820</v>
       </c>
       <c r="B151" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>136114822</v>
       </c>
       <c r="B152" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>136114823</v>
       </c>
       <c r="B153" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93405</v>
+        <v>93408</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93428</v>
+        <v>93431</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101574</v>
+        <v>101575</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>136114818</v>
       </c>
       <c r="B90" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>136114819</v>
       </c>
       <c r="B91" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136114825</v>
       </c>
       <c r="B92" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>136114826</v>
       </c>
       <c r="B93" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>136114821</v>
       </c>
       <c r="B112" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>136114827</v>
       </c>
       <c r="B113" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>136114824</v>
       </c>
       <c r="B115" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>136114817</v>
       </c>
       <c r="B131" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>136114820</v>
       </c>
       <c r="B151" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>136114822</v>
       </c>
       <c r="B152" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>136114823</v>
       </c>
       <c r="B153" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101575</v>
+        <v>101580</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>136114818</v>
       </c>
       <c r="B90" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>136114819</v>
       </c>
       <c r="B91" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136114825</v>
       </c>
       <c r="B92" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>136114826</v>
       </c>
       <c r="B93" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>136114821</v>
       </c>
       <c r="B112" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>136114827</v>
       </c>
       <c r="B113" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>136114824</v>
       </c>
       <c r="B115" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>136114817</v>
       </c>
       <c r="B131" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>136114820</v>
       </c>
       <c r="B151" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>136114822</v>
       </c>
       <c r="B152" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>136114823</v>
       </c>
       <c r="B153" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93409</v>
+        <v>93414</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93432</v>
+        <v>93437</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101580</v>
+        <v>101582</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93414</v>
+        <v>93416</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93414</v>
+        <v>93416</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93414</v>
+        <v>93416</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93414</v>
+        <v>93416</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93414</v>
+        <v>93416</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93414</v>
+        <v>93416</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93416</v>
+        <v>93418</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93416</v>
+        <v>93418</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93416</v>
+        <v>93418</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93416</v>
+        <v>93418</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93416</v>
+        <v>93418</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93416</v>
+        <v>93418</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87377</v>
+        <v>87378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87377</v>
+        <v>87378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87327</v>
+        <v>87328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>136431854</v>
       </c>
       <c r="B167" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>136431855</v>
       </c>
       <c r="B168" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>136431856</v>
       </c>
       <c r="B169" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>136431857</v>
       </c>
       <c r="B170" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93420</v>
+        <v>93421</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87378</v>
+        <v>87384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87378</v>
+        <v>87384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87328</v>
+        <v>87334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93421</v>
+        <v>93427</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87384</v>
+        <v>87388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87384</v>
+        <v>87388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87334</v>
+        <v>87338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93427</v>
+        <v>93431</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87388</v>
+        <v>87390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87388</v>
+        <v>87390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87338</v>
+        <v>87340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87390</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87390</v>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87340</v>
+        <v>87353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93433</v>
+        <v>93446</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87403</v>
+        <v>87405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87353</v>
+        <v>87355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87405</v>
+        <v>87408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87405</v>
+        <v>87408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137084841</v>
       </c>
       <c r="B16" t="n">
-        <v>87355</v>
+        <v>87358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>137084831</v>
       </c>
       <c r="B99" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>137084832</v>
       </c>
       <c r="B100" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>137084834</v>
       </c>
       <c r="B101" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>137084838</v>
       </c>
       <c r="B102" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137084840</v>
       </c>
       <c r="B103" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>137084825</v>
       </c>
       <c r="B139" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>137084835</v>
       </c>
       <c r="B142" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>137084833</v>
       </c>
       <c r="B144" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>137084822</v>
       </c>
       <c r="B171" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>137084823</v>
       </c>
       <c r="B172" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>137084824</v>
       </c>
       <c r="B173" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>137084826</v>
       </c>
       <c r="B174" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>137084827</v>
       </c>
       <c r="B175" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>137084828</v>
       </c>
       <c r="B176" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>137084829</v>
       </c>
       <c r="B177" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>137084853</v>
       </c>
       <c r="B178" t="n">
-        <v>93447</v>
+        <v>93450</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87368</v>
+        <v>87369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87368</v>
+        <v>87369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93460</v>
+        <v>93461</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87369</v>
+        <v>87372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87369</v>
+        <v>87372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93461</v>
+        <v>93466</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93466</v>
+        <v>93468</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87372</v>
+        <v>87377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87372</v>
+        <v>87377</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93468</v>
+        <v>93474</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87377</v>
+        <v>87388</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87377</v>
+        <v>87388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93474</v>
+        <v>93486</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87388</v>
+        <v>87389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87388</v>
+        <v>87389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87389</v>
+        <v>87392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87389</v>
+        <v>87392</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93487</v>
+        <v>93490</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137084821</v>
       </c>
       <c r="B3" t="n">
-        <v>87442</v>
+        <v>87446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137084852</v>
       </c>
       <c r="B4" t="n">
-        <v>87442</v>
+        <v>87446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137296815</v>
       </c>
       <c r="B5" t="n">
-        <v>87442</v>
+        <v>87446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>137084841</v>
       </c>
       <c r="B17" t="n">
-        <v>87392</v>
+        <v>87396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>137296790</v>
       </c>
       <c r="B18" t="n">
-        <v>87392</v>
+        <v>87396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>137084831</v>
       </c>
       <c r="B101" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>137084832</v>
       </c>
       <c r="B102" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>137084834</v>
       </c>
       <c r="B103" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>137084838</v>
       </c>
       <c r="B104" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>137084840</v>
       </c>
       <c r="B105" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>137084825</v>
       </c>
       <c r="B141" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>137084835</v>
       </c>
       <c r="B144" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>137084833</v>
       </c>
       <c r="B146" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>137084822</v>
       </c>
       <c r="B173" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>137084823</v>
       </c>
       <c r="B174" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>137084824</v>
       </c>
       <c r="B175" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>137084826</v>
       </c>
       <c r="B176" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>137084827</v>
       </c>
       <c r="B177" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>137084828</v>
       </c>
       <c r="B178" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>137084829</v>
       </c>
       <c r="B179" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>137084853</v>
       </c>
       <c r="B180" t="n">
-        <v>93490</v>
+        <v>93494</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
